--- a/PaHaW/PaHaW/PaHaW_files/corpus_PaHaW.xlsx
+++ b/PaHaW/PaHaW/PaHaW_files/corpus_PaHaW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evmagante\Downloads\PaHaW\PaHaW\PaHaW_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE43E212-2B7B-4F19-85BE-EC81721E4AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D27CE71B-D8D3-4453-8EE1-A2940D14240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="86">
   <si>
     <t>00001</t>
   </si>
@@ -84,9 +84,6 @@
     <t>00010</t>
   </si>
   <si>
-    <t>00013</t>
-  </si>
-  <si>
     <t>00014</t>
   </si>
   <si>
@@ -111,15 +108,9 @@
     <t>00022</t>
   </si>
   <si>
-    <t>00023</t>
-  </si>
-  <si>
     <t>00024</t>
   </si>
   <si>
-    <t>00025</t>
-  </si>
-  <si>
     <t>00026</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
     <t>00039</t>
   </si>
   <si>
-    <t>00040</t>
-  </si>
-  <si>
     <t>00041</t>
   </si>
   <si>
@@ -186,9 +174,6 @@
     <t>00054</t>
   </si>
   <si>
-    <t>00055</t>
-  </si>
-  <si>
     <t>00057</t>
   </si>
   <si>
@@ -214,9 +199,6 @@
   </si>
   <si>
     <t>00071</t>
-  </si>
-  <si>
-    <t>00072</t>
   </si>
   <si>
     <t>00073</t>
@@ -692,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.09765625" bestFit="1" customWidth="1"/>
@@ -709,34 +691,34 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -812,7 +794,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
@@ -827,34 +809,34 @@
         <v>4</v>
       </c>
       <c r="F4" s="3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="3">
-        <v>990</v>
+        <v>1080</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="3">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <f t="shared" ref="K4:K67" si="0">K3+1</f>
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="K4" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
@@ -863,28 +845,28 @@
         <v>4</v>
       </c>
       <c r="F5" s="3">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <v>1080</v>
+        <v>397.5</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="3">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="K5" t="e">
+        <f t="shared" ref="K5:K61" si="0">K4+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>1</v>
@@ -899,28 +881,28 @@
         <v>4</v>
       </c>
       <c r="F6" s="3">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="3">
-        <v>397.5</v>
+        <v>1115</v>
       </c>
       <c r="I6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="K6" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>1</v>
@@ -935,28 +917,28 @@
         <v>4</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <v>1115</v>
+        <v>2110</v>
       </c>
       <c r="I7" s="5">
         <v>2</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="K7" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>1</v>
@@ -971,28 +953,28 @@
         <v>4</v>
       </c>
       <c r="F8" s="3">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="3">
-        <v>2110</v>
+        <v>1556.6</v>
       </c>
       <c r="I8" s="5">
         <v>2</v>
       </c>
       <c r="J8" s="3">
-        <v>8</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
         <v>7</v>
+      </c>
+      <c r="K8" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>1</v>
@@ -1007,28 +989,28 @@
         <v>4</v>
       </c>
       <c r="F9" s="3">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="3">
-        <v>1556.6</v>
+        <v>1691</v>
       </c>
       <c r="I9" s="5">
         <v>2</v>
       </c>
       <c r="J9" s="3">
-        <v>7</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="K9" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
@@ -1043,70 +1025,70 @@
         <v>4</v>
       </c>
       <c r="F10" s="3">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H10" s="3">
-        <v>1691</v>
+        <v>600</v>
       </c>
       <c r="I10" s="5">
         <v>2</v>
       </c>
       <c r="J10" s="3">
-        <v>12</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="K10" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>57</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1271.6600000000001</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3">
-        <v>69</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="3">
-        <v>600</v>
-      </c>
-      <c r="I11" s="5">
-        <v>2</v>
-      </c>
-      <c r="J11" s="3">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+      <c r="K11" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
@@ -1115,34 +1097,34 @@
         <v>4</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3">
-        <v>1271.6600000000001</v>
+        <v>1187.5</v>
       </c>
       <c r="I12" s="5">
         <v>2</v>
       </c>
       <c r="J12" s="3">
-        <v>9</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="K12" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>3</v>
@@ -1151,23 +1133,23 @@
         <v>4</v>
       </c>
       <c r="F13" s="3">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3">
-        <v>1187.5</v>
+        <v>750</v>
       </c>
       <c r="I13" s="5">
         <v>2</v>
       </c>
       <c r="J13" s="3">
-        <v>4</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="K13" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1187,23 +1169,23 @@
         <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>750</v>
+        <v>2226.66</v>
       </c>
       <c r="I14" s="5">
         <v>2</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="K14" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1223,28 +1205,28 @@
         <v>4</v>
       </c>
       <c r="F15" s="3">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H15" s="3">
-        <v>2226.66</v>
+        <v>645</v>
       </c>
       <c r="I15" s="5">
         <v>2</v>
       </c>
       <c r="J15" s="3">
-        <v>8</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="K15" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1</v>
@@ -1259,34 +1241,34 @@
         <v>4</v>
       </c>
       <c r="F16" s="3">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="3">
-        <v>645</v>
+        <v>750</v>
       </c>
       <c r="I16" s="5">
         <v>2</v>
       </c>
       <c r="J16" s="3">
-        <v>14</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="K16" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>3</v>
@@ -1295,34 +1277,34 @@
         <v>4</v>
       </c>
       <c r="F17" s="3">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="3">
-        <v>1235</v>
+        <v>2546.66</v>
       </c>
       <c r="I17" s="5">
         <v>2</v>
       </c>
       <c r="J17" s="3">
-        <v>9</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="K17" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>3</v>
@@ -1331,7 +1313,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="3">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>5</v>
@@ -1343,16 +1325,16 @@
         <v>2</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="K18" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>1</v>
@@ -1367,28 +1349,28 @@
         <v>4</v>
       </c>
       <c r="F19" s="3">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H19" s="3">
-        <v>2546.66</v>
+        <v>1941.66</v>
       </c>
       <c r="I19" s="5">
         <v>2</v>
       </c>
       <c r="J19" s="3">
-        <v>5</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>2</v>
+      </c>
+      <c r="K19" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1</v>
@@ -1403,28 +1385,28 @@
         <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>750</v>
+        <v>2546</v>
       </c>
       <c r="I20" s="5">
         <v>2</v>
       </c>
       <c r="J20" s="3">
-        <v>3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="K20" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
@@ -1439,34 +1421,34 @@
         <v>4</v>
       </c>
       <c r="F21" s="3">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="3">
-        <v>1941.66</v>
+        <v>800</v>
       </c>
       <c r="I21" s="5">
         <v>2</v>
       </c>
       <c r="J21" s="3">
-        <v>2</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="K21" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
@@ -1475,28 +1457,28 @@
         <v>4</v>
       </c>
       <c r="F22" s="3">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="3">
-        <v>2546</v>
+        <v>1210</v>
       </c>
       <c r="I22" s="5">
         <v>2</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="K22" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>1</v>
@@ -1511,28 +1493,28 @@
         <v>4</v>
       </c>
       <c r="F23" s="3">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H23" s="3">
-        <v>800</v>
-      </c>
-      <c r="I23" s="5">
-        <v>2</v>
+        <v>1480</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2.5</v>
       </c>
       <c r="J23" s="3">
-        <v>12</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="K23" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>1</v>
@@ -1547,34 +1529,34 @@
         <v>4</v>
       </c>
       <c r="F24" s="3">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H24" s="3">
-        <v>1210</v>
-      </c>
-      <c r="I24" s="5">
-        <v>2</v>
+        <v>990</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2.5</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="K24" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>3</v>
@@ -1583,34 +1565,34 @@
         <v>4</v>
       </c>
       <c r="F25" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="3">
-        <v>1480</v>
+        <v>1250</v>
       </c>
       <c r="I25" s="4">
         <v>2.5</v>
       </c>
       <c r="J25" s="3">
-        <v>3</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="K25" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>3</v>
@@ -1619,34 +1601,34 @@
         <v>4</v>
       </c>
       <c r="F26" s="3">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="3">
-        <v>990</v>
+        <v>2386.66</v>
       </c>
       <c r="I26" s="4">
         <v>2.5</v>
       </c>
       <c r="J26" s="3">
-        <v>17</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="K26" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>3</v>
@@ -1655,34 +1637,34 @@
         <v>4</v>
       </c>
       <c r="F27" s="3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H27" s="3">
-        <v>1250</v>
+        <v>2010</v>
       </c>
       <c r="I27" s="4">
         <v>2.5</v>
       </c>
       <c r="J27" s="3">
-        <v>17</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="K27" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>3</v>
@@ -1691,28 +1673,28 @@
         <v>4</v>
       </c>
       <c r="F28" s="3">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H28" s="3">
-        <v>1930</v>
+        <v>666.66</v>
       </c>
       <c r="I28" s="4">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J28" s="3">
-        <v>14</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>19</v>
+      </c>
+      <c r="K28" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>1</v>
@@ -1727,28 +1709,28 @@
         <v>4</v>
       </c>
       <c r="F29" s="3">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H29" s="3">
-        <v>2386.66</v>
+        <v>1253.33</v>
       </c>
       <c r="I29" s="4">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J29" s="3">
-        <v>9</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="K29" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>1</v>
@@ -1763,34 +1745,34 @@
         <v>4</v>
       </c>
       <c r="F30" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H30" s="3">
-        <v>2010</v>
+        <v>2336.66</v>
       </c>
       <c r="I30" s="4">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J30" s="3">
-        <v>12</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <v>13</v>
+      </c>
+      <c r="K30" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>11</v>
+      <c r="A31" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>3</v>
@@ -1799,28 +1781,28 @@
         <v>4</v>
       </c>
       <c r="F31" s="3">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H31" s="3">
-        <v>666.66</v>
+        <v>3544.16</v>
       </c>
       <c r="I31" s="4">
         <v>3</v>
       </c>
       <c r="J31" s="3">
-        <v>19</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="K31" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>1</v>
@@ -1835,28 +1817,28 @@
         <v>4</v>
       </c>
       <c r="F32" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H32" s="3">
-        <v>1253.33</v>
-      </c>
-      <c r="I32" s="4">
-        <v>3</v>
+        <v>1316.66</v>
+      </c>
+      <c r="I32" s="6">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
-        <v>8</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <v>7</v>
+      </c>
+      <c r="K32" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>1</v>
@@ -1871,34 +1853,34 @@
         <v>4</v>
       </c>
       <c r="F33" s="3">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H33" s="3">
-        <v>1143</v>
-      </c>
-      <c r="I33" s="4">
-        <v>3</v>
+        <v>1450</v>
+      </c>
+      <c r="I33" s="6">
+        <v>4</v>
       </c>
       <c r="J33" s="3">
-        <v>10</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="K33" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>3</v>
@@ -1907,64 +1889,53 @@
         <v>4</v>
       </c>
       <c r="F34" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H34" s="3">
-        <v>2336.66</v>
-      </c>
-      <c r="I34" s="4">
-        <v>3</v>
+        <v>1370</v>
+      </c>
+      <c r="I34" s="6">
+        <v>5</v>
       </c>
       <c r="J34" s="3">
-        <v>13</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <v>18</v>
+      </c>
+      <c r="K34" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
-        <v>67</v>
+      <c r="A35" t="s">
+        <v>25</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F35" s="3">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H35" s="3">
-        <v>3544.16</v>
-      </c>
-      <c r="I35" s="4">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
-        <v>5</v>
-      </c>
-      <c r="K35" s="8">
-        <f t="shared" si="0"/>
-        <v>34</v>
+      <c r="I35" s="7"/>
+      <c r="K35" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>1</v>
@@ -1973,70 +1944,48 @@
         <v>14</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F36" s="3">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H36" s="3">
-        <v>1316.66</v>
-      </c>
-      <c r="I36" s="6">
-        <v>4</v>
-      </c>
-      <c r="J36" s="3">
-        <v>7</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="0"/>
-        <v>35</v>
+      <c r="I36" s="7"/>
+      <c r="K36" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F37" s="3">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H37" s="3">
-        <v>1450</v>
-      </c>
-      <c r="I37" s="6">
-        <v>4</v>
-      </c>
-      <c r="J37" s="3">
-        <v>12</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="0"/>
-        <v>36</v>
+      <c r="I37" s="7"/>
+      <c r="K37" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>1</v>
@@ -2045,59 +1994,48 @@
         <v>2</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F38" s="3">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H38" s="3">
-        <v>1370</v>
-      </c>
-      <c r="I38" s="6">
-        <v>5</v>
-      </c>
-      <c r="J38" s="3">
-        <v>18</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="0"/>
-        <v>37</v>
+      <c r="I38" s="7"/>
+      <c r="K38" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F39" s="3">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I39" s="7"/>
-      <c r="K39">
-        <f t="shared" si="0"/>
-        <v>38</v>
+      <c r="K39" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>1</v>
@@ -2106,23 +2044,23 @@
         <v>14</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F40" s="3">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I40" s="7"/>
-      <c r="K40">
-        <f t="shared" si="0"/>
-        <v>39</v>
+      <c r="K40" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>1</v>
@@ -2131,48 +2069,48 @@
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F41" s="3">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I41" s="7"/>
-      <c r="K41">
-        <f t="shared" si="0"/>
-        <v>40</v>
+      <c r="K41" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F42" s="3">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I42" s="7"/>
-      <c r="K42">
-        <f t="shared" si="0"/>
-        <v>41</v>
+      <c r="K42" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>1</v>
@@ -2181,23 +2119,23 @@
         <v>14</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F43" s="3">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I43" s="7"/>
-      <c r="K43">
-        <f t="shared" si="0"/>
-        <v>42</v>
+      <c r="K43" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>1</v>
@@ -2206,23 +2144,23 @@
         <v>14</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F44" s="3">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I44" s="7"/>
-      <c r="K44">
-        <f t="shared" si="0"/>
-        <v>43</v>
+      <c r="K44" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>1</v>
@@ -2231,48 +2169,48 @@
         <v>2</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F45" s="3">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I45" s="7"/>
-      <c r="K45">
-        <f t="shared" si="0"/>
-        <v>44</v>
+      <c r="K45" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F46" s="3">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I46" s="7"/>
-      <c r="K46">
-        <f t="shared" si="0"/>
-        <v>45</v>
+      <c r="K46" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>1</v>
@@ -2281,23 +2219,23 @@
         <v>14</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I47" s="7"/>
-      <c r="K47">
-        <f t="shared" si="0"/>
-        <v>46</v>
+      <c r="K47" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>1</v>
@@ -2306,48 +2244,48 @@
         <v>14</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F48" s="3">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I48" s="7"/>
-      <c r="K48">
-        <f t="shared" si="0"/>
-        <v>47</v>
+      <c r="K48" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>45</v>
+      <c r="A49" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F49" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I49" s="7"/>
-      <c r="K49">
-        <f t="shared" si="0"/>
-        <v>48</v>
+      <c r="K49" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>1</v>
@@ -2356,23 +2294,23 @@
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F50" s="3">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I50" s="7"/>
-      <c r="K50">
-        <f t="shared" si="0"/>
-        <v>49</v>
+      <c r="K50" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>1</v>
@@ -2381,18 +2319,18 @@
         <v>2</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F51" s="3">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I51" s="7"/>
-      <c r="K51">
-        <f t="shared" si="0"/>
-        <v>50</v>
+      <c r="K51" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
@@ -2406,18 +2344,18 @@
         <v>14</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F52" s="3">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I52" s="7"/>
-      <c r="K52">
-        <f t="shared" si="0"/>
-        <v>51</v>
+      <c r="K52" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
@@ -2428,25 +2366,25 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F53" s="3">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I53" s="7"/>
-      <c r="K53">
-        <f t="shared" si="0"/>
-        <v>52</v>
+      <c r="K53" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
+      <c r="A54" t="s">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -2456,18 +2394,18 @@
         <v>2</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F54" s="3">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I54" s="7"/>
-      <c r="K54">
-        <f t="shared" si="0"/>
-        <v>53</v>
+      <c r="K54" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -2478,21 +2416,21 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F55" s="3">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I55" s="7"/>
-      <c r="K55">
-        <f t="shared" si="0"/>
-        <v>54</v>
+      <c r="K55" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -2506,73 +2444,73 @@
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F56" s="3">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I56" s="7"/>
-      <c r="K56">
-        <f t="shared" si="0"/>
-        <v>55</v>
+      <c r="K56" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F57" s="3">
-        <v>59</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I57" s="7"/>
-      <c r="K57">
-        <f t="shared" si="0"/>
-        <v>56</v>
+      <c r="K57" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58" s="3">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I58" s="7"/>
-      <c r="K58">
-        <f t="shared" si="0"/>
-        <v>57</v>
+      <c r="K58" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>1</v>
@@ -2581,98 +2519,98 @@
         <v>2</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F59" s="3">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I59" s="7"/>
-      <c r="K59">
-        <f t="shared" si="0"/>
-        <v>58</v>
+      <c r="K59" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F60" s="3">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I60" s="7"/>
-      <c r="K60">
-        <f t="shared" si="0"/>
-        <v>59</v>
+      <c r="K60" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F61" s="3">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I61" s="7"/>
-      <c r="K61">
-        <f t="shared" si="0"/>
-        <v>60</v>
+      <c r="K61" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F62" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I62" s="7"/>
-      <c r="K62">
-        <f t="shared" si="0"/>
-        <v>61</v>
+      <c r="K62" t="e">
+        <f t="shared" ref="K62:K70" si="1">K61+1</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>64</v>
+      <c r="A63" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>1</v>
@@ -2681,18 +2619,18 @@
         <v>14</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F63" s="3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I63" s="7"/>
-      <c r="K63">
-        <f t="shared" si="0"/>
-        <v>62</v>
+      <c r="K63" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
@@ -2706,18 +2644,18 @@
         <v>14</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F64" s="3">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I64" s="7"/>
-      <c r="K64">
-        <f t="shared" si="0"/>
-        <v>63</v>
+      <c r="K64" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
@@ -2731,18 +2669,18 @@
         <v>2</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I65" s="7"/>
-      <c r="K65">
-        <f t="shared" si="0"/>
-        <v>64</v>
+      <c r="K65" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
@@ -2756,18 +2694,18 @@
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F66" s="3">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I66" s="7"/>
-      <c r="K66">
-        <f t="shared" si="0"/>
-        <v>65</v>
+      <c r="K66" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
@@ -2778,21 +2716,21 @@
         <v>1</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F67" s="3">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I67" s="7"/>
-      <c r="K67">
-        <f t="shared" si="0"/>
-        <v>66</v>
+      <c r="K67" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
@@ -2806,43 +2744,43 @@
         <v>14</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F68" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I68" s="7"/>
-      <c r="K68">
-        <f t="shared" ref="K68:K76" si="1">K67+1</f>
-        <v>67</v>
+      <c r="K68" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="9" t="s">
+      <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F69" s="3">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I69" s="7"/>
-      <c r="K69">
+      <c r="K69" t="e">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
@@ -2856,173 +2794,23 @@
         <v>14</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F70" s="3">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I70" s="7"/>
-      <c r="K70">
+      <c r="K70" t="e">
         <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F71" s="3">
-        <v>64</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I71" s="7"/>
-      <c r="K71">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F72" s="3">
-        <v>58</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="7"/>
-      <c r="K72">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F73" s="3">
-        <v>64</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I73" s="7"/>
-      <c r="K73">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F74" s="3">
-        <v>74</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I74" s="7"/>
-      <c r="K74">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>79</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F75" s="3">
-        <v>77</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I75" s="7"/>
-      <c r="K75">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F76" s="3">
-        <v>44</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="7"/>
-      <c r="K76">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J76">
-    <sortCondition ref="I2:I76"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J70">
+    <sortCondition ref="I2:I70"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
